--- a/artfynd/A 36260-2023 artfynd.xlsx
+++ b/artfynd/A 36260-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 36260-2023 artfynd.xlsx
+++ b/artfynd/A 36260-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113703449</v>
+        <v>113703454</v>
       </c>
       <c r="B2" t="n">
-        <v>91263</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4769</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Jämtlands län, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>411885</v>
+        <v>411793</v>
       </c>
       <c r="R2" t="n">
-        <v>7021286</v>
+        <v>7021382</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Måttligt på rn låga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113703438</v>
+        <v>113703448</v>
       </c>
       <c r="B3" t="n">
-        <v>102557</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,34 +792,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222002</v>
+        <v>4769</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Jämtlands län, Jmt</t>
+          <t>Henåns delta, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>411951</v>
+        <v>411934</v>
       </c>
       <c r="R3" t="n">
-        <v>7021327</v>
+        <v>7021277</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,11 +852,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-09-30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt. Granskog intill undersåkersälven</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,15 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113703452</v>
+        <v>113703449</v>
       </c>
       <c r="B4" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -912,34 +893,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Jämtlands län, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>411919</v>
+        <v>411885</v>
       </c>
       <c r="R4" t="n">
-        <v>7021287</v>
+        <v>7021286</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,11 +957,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-09-30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Påtagligt på en högstbbe o låga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,15 +987,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113703448</v>
+        <v>113703500</v>
       </c>
       <c r="B5" t="n">
-        <v>91263</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,20 +1012,24 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Henåns delta, Jmt</t>
+          <t>Jämtlands län, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>411934</v>
+        <v>411830</v>
       </c>
       <c r="R5" t="n">
-        <v>7021277</v>
+        <v>7021355</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,15 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113703500</v>
+        <v>113703452</v>
       </c>
       <c r="B6" t="n">
-        <v>91263</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1129,38 +1103,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Jämtlands län, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>411830</v>
+        <v>411919</v>
       </c>
       <c r="R6" t="n">
-        <v>7021355</v>
+        <v>7021287</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,6 +1165,11 @@
           <t>2023-09-30</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påtagligt på en högstbbe o låga</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1216,6 +1191,112 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>113703438</v>
+      </c>
+      <c r="B7" t="n">
+        <v>103683</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Jämtlands län, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>411951</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7021327</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt. Granskog intill undersåkersälven</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Eva Romell</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>

--- a/artfynd/A 36260-2023 artfynd.xlsx
+++ b/artfynd/A 36260-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113703454</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113703448</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -984,6 +999,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113703449</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1089,6 +1109,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113703500</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1195,6 +1220,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113703452</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1301,8 +1331,21 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113703438</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>